--- a/others/Vinson-norm_filtered.xlsx
+++ b/others/Vinson-norm_filtered.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_ALEX_\RESEARCH\MRNGO\A_conceptnorm\data\school-pilot\others\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_ALEX_\RESEARCH\MRNGO\A_conceptnorm\data\MRNGO_mini-norm\others\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACD7B967-7D45-4B71-9B0C-DC5AD0F894A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{427D8A6D-02E9-403D-AB30-B91C7BE9773A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1515" yWindow="690" windowWidth="21600" windowHeight="12450" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="features" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1592" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="421">
   <si>
     <t>Concept</t>
   </si>
@@ -1091,31 +1091,13 @@
     <t>salt</t>
   </si>
   <si>
-    <t>RUG</t>
-  </si>
-  <si>
-    <t>beat</t>
-  </si>
-  <si>
     <t>buy</t>
   </si>
   <si>
-    <t>carpet</t>
-  </si>
-  <si>
     <t>flat</t>
   </si>
   <si>
-    <t>mud</t>
-  </si>
-  <si>
-    <t>shoe</t>
-  </si>
-  <si>
     <t>sit</t>
-  </si>
-  <si>
-    <t>store</t>
   </si>
   <si>
     <t>SHOE</t>
@@ -1664,7 +1646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C786"/>
+  <dimension ref="A1:C758"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -7961,21 +7943,21 @@
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
-        <v>356</v>
-      </c>
-      <c r="B573" t="s">
-        <v>357</v>
+        <v>359</v>
+      </c>
+      <c r="B573">
+        <v>2</v>
       </c>
       <c r="C573">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B574" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C574">
         <v>1</v>
@@ -7983,65 +7965,65 @@
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B575" t="s">
-        <v>359</v>
+        <v>35</v>
       </c>
       <c r="C575">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B576" t="s">
-        <v>146</v>
+        <v>361</v>
       </c>
       <c r="C576">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B577" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="C577">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B578" t="s">
-        <v>149</v>
+        <v>328</v>
       </c>
       <c r="C578">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B579" t="s">
-        <v>41</v>
+        <v>215</v>
       </c>
       <c r="C579">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B580" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="C580">
         <v>1</v>
@@ -8049,10 +8031,10 @@
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B581" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C581">
         <v>2</v>
@@ -8060,10 +8042,10 @@
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B582" t="s">
-        <v>102</v>
+        <v>362</v>
       </c>
       <c r="C582">
         <v>1</v>
@@ -8071,120 +8053,120 @@
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B583" t="s">
-        <v>360</v>
+        <v>42</v>
       </c>
       <c r="C583">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B584" t="s">
-        <v>103</v>
+        <v>363</v>
       </c>
       <c r="C584">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B585" t="s">
         <v>197</v>
       </c>
       <c r="C585">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B586" t="s">
-        <v>105</v>
+        <v>352</v>
       </c>
       <c r="C586">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B587" t="s">
-        <v>152</v>
+        <v>331</v>
       </c>
       <c r="C587">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B588" t="s">
-        <v>361</v>
+        <v>45</v>
       </c>
       <c r="C588">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B589" t="s">
-        <v>76</v>
+        <v>364</v>
       </c>
       <c r="C589">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B590" t="s">
-        <v>157</v>
+        <v>108</v>
       </c>
       <c r="C590">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B591" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="C591">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B592" t="s">
-        <v>362</v>
+        <v>76</v>
       </c>
       <c r="C592">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B593" t="s">
-        <v>363</v>
+        <v>136</v>
       </c>
       <c r="C593">
         <v>1</v>
@@ -8192,98 +8174,98 @@
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B594" t="s">
-        <v>24</v>
+        <v>157</v>
       </c>
       <c r="C594">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B595" t="s">
-        <v>158</v>
+        <v>365</v>
       </c>
       <c r="C595">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B596" t="s">
-        <v>84</v>
+        <v>366</v>
       </c>
       <c r="C596">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B597" t="s">
-        <v>364</v>
+        <v>298</v>
       </c>
       <c r="C597">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B598" t="s">
-        <v>87</v>
+        <v>25</v>
       </c>
       <c r="C598">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B599" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="C599">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B600" t="s">
-        <v>162</v>
+        <v>367</v>
       </c>
       <c r="C600">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
-        <v>365</v>
-      </c>
-      <c r="B601">
-        <v>2</v>
+        <v>359</v>
+      </c>
+      <c r="B601" t="s">
+        <v>302</v>
       </c>
       <c r="C601">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="B602" t="s">
-        <v>366</v>
+        <v>205</v>
       </c>
       <c r="C602">
         <v>1</v>
@@ -8291,32 +8273,32 @@
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="B603" t="s">
-        <v>35</v>
+        <v>188</v>
       </c>
       <c r="C603">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="B604" t="s">
-        <v>367</v>
+        <v>161</v>
       </c>
       <c r="C604">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="B605" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="C605">
         <v>1</v>
@@ -8324,54 +8306,54 @@
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="B606" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="C606">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B607" t="s">
-        <v>215</v>
+        <v>369</v>
       </c>
       <c r="C607">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B608" t="s">
-        <v>147</v>
+        <v>7</v>
       </c>
       <c r="C608">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B609" t="s">
-        <v>59</v>
+        <v>370</v>
       </c>
       <c r="C609">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B610" t="s">
-        <v>368</v>
+        <v>311</v>
       </c>
       <c r="C610">
         <v>1</v>
@@ -8379,54 +8361,54 @@
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B611" t="s">
-        <v>42</v>
+        <v>371</v>
       </c>
       <c r="C611">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B612" t="s">
-        <v>369</v>
+        <v>8</v>
       </c>
       <c r="C612">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B613" t="s">
-        <v>197</v>
+        <v>9</v>
       </c>
       <c r="C613">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B614" t="s">
-        <v>352</v>
+        <v>43</v>
       </c>
       <c r="C614">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B615" t="s">
-        <v>331</v>
+        <v>67</v>
       </c>
       <c r="C615">
         <v>1</v>
@@ -8434,21 +8416,21 @@
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B616" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="C616">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B617" t="s">
-        <v>370</v>
+        <v>105</v>
       </c>
       <c r="C617">
         <v>3</v>
@@ -8456,21 +8438,21 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B618" t="s">
-        <v>108</v>
+        <v>11</v>
       </c>
       <c r="C618">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B619" t="s">
-        <v>75</v>
+        <v>179</v>
       </c>
       <c r="C619">
         <v>1</v>
@@ -8478,21 +8460,21 @@
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B620" t="s">
-        <v>76</v>
+        <v>353</v>
       </c>
       <c r="C620">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B621" t="s">
-        <v>136</v>
+        <v>372</v>
       </c>
       <c r="C621">
         <v>1</v>
@@ -8500,21 +8482,21 @@
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B622" t="s">
-        <v>157</v>
+        <v>13</v>
       </c>
       <c r="C622">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B623" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C623">
         <v>1</v>
@@ -8522,32 +8504,32 @@
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B624" t="s">
-        <v>372</v>
+        <v>15</v>
       </c>
       <c r="C624">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B625" t="s">
-        <v>298</v>
+        <v>16</v>
       </c>
       <c r="C625">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B626" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="C626">
         <v>2</v>
@@ -8555,10 +8537,10 @@
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B627" t="s">
-        <v>139</v>
+        <v>374</v>
       </c>
       <c r="C627">
         <v>1</v>
@@ -8566,87 +8548,87 @@
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B628" t="s">
-        <v>373</v>
+        <v>18</v>
       </c>
       <c r="C628">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B629" t="s">
-        <v>302</v>
+        <v>21</v>
       </c>
       <c r="C629">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B630" t="s">
-        <v>205</v>
+        <v>24</v>
       </c>
       <c r="C630">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B631" t="s">
-        <v>188</v>
+        <v>25</v>
       </c>
       <c r="C631">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B632" t="s">
-        <v>161</v>
+        <v>28</v>
       </c>
       <c r="C632">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B633" t="s">
-        <v>162</v>
+        <v>29</v>
       </c>
       <c r="C633">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B634" t="s">
-        <v>334</v>
+        <v>375</v>
       </c>
       <c r="C634">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="B635" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C635">
         <v>1</v>
@@ -8654,87 +8636,87 @@
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="B636" t="s">
-        <v>7</v>
+        <v>323</v>
       </c>
       <c r="C636">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="B637" t="s">
-        <v>376</v>
+        <v>32</v>
       </c>
       <c r="C637">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B638" t="s">
-        <v>311</v>
+        <v>232</v>
       </c>
       <c r="C638">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B639" t="s">
-        <v>377</v>
+        <v>356</v>
       </c>
       <c r="C639">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B640" t="s">
-        <v>8</v>
+        <v>378</v>
       </c>
       <c r="C640">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B641" t="s">
-        <v>9</v>
+        <v>146</v>
       </c>
       <c r="C641">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B642" t="s">
-        <v>43</v>
+        <v>328</v>
       </c>
       <c r="C642">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B643" t="s">
-        <v>67</v>
+        <v>329</v>
       </c>
       <c r="C643">
         <v>1</v>
@@ -8742,10 +8724,10 @@
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B644" t="s">
-        <v>10</v>
+        <v>147</v>
       </c>
       <c r="C644">
         <v>4</v>
@@ -8753,32 +8735,32 @@
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B645" t="s">
-        <v>105</v>
+        <v>330</v>
       </c>
       <c r="C645">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B646" t="s">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="C646">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B647" t="s">
-        <v>179</v>
+        <v>379</v>
       </c>
       <c r="C647">
         <v>1</v>
@@ -8786,54 +8768,54 @@
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B648" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="C648">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B649" t="s">
-        <v>378</v>
+        <v>130</v>
       </c>
       <c r="C649">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B650" t="s">
-        <v>13</v>
+        <v>380</v>
       </c>
       <c r="C650">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B651" t="s">
-        <v>379</v>
+        <v>45</v>
       </c>
       <c r="C651">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B652" t="s">
-        <v>15</v>
+        <v>154</v>
       </c>
       <c r="C652">
         <v>2</v>
@@ -8841,21 +8823,21 @@
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B653" t="s">
-        <v>16</v>
+        <v>381</v>
       </c>
       <c r="C653">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B654" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="C654">
         <v>2</v>
@@ -8863,131 +8845,131 @@
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B655" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C655">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B656" t="s">
-        <v>18</v>
+        <v>158</v>
       </c>
       <c r="C656">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B657" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="C657">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B658" t="s">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="C658">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B659" t="s">
-        <v>25</v>
+        <v>303</v>
       </c>
       <c r="C659">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B660" t="s">
-        <v>28</v>
+        <v>383</v>
       </c>
       <c r="C660">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B661" t="s">
-        <v>29</v>
+        <v>162</v>
       </c>
       <c r="C661">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B662" t="s">
-        <v>381</v>
+        <v>334</v>
       </c>
       <c r="C662">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B663" t="s">
-        <v>382</v>
+        <v>335</v>
       </c>
       <c r="C663">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B664" t="s">
-        <v>323</v>
+        <v>384</v>
       </c>
       <c r="C664">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="B665" t="s">
-        <v>32</v>
+        <v>254</v>
       </c>
       <c r="C665">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B666" t="s">
-        <v>232</v>
+        <v>386</v>
       </c>
       <c r="C666">
         <v>2</v>
@@ -8995,428 +8977,428 @@
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B667" t="s">
-        <v>358</v>
+        <v>387</v>
       </c>
       <c r="C667">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B668" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C668">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B669" t="s">
-        <v>146</v>
+        <v>389</v>
       </c>
       <c r="C669">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B670" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="C670">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B671" t="s">
-        <v>329</v>
+        <v>106</v>
       </c>
       <c r="C671">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B672" t="s">
-        <v>147</v>
+        <v>292</v>
       </c>
       <c r="C672">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B673" t="s">
-        <v>330</v>
+        <v>391</v>
       </c>
       <c r="C673">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="674" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B674" t="s">
-        <v>59</v>
+        <v>392</v>
       </c>
       <c r="C674">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B675" t="s">
-        <v>385</v>
+        <v>72</v>
       </c>
       <c r="C675">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B676" t="s">
-        <v>369</v>
+        <v>47</v>
       </c>
       <c r="C676">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="677" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B677" t="s">
-        <v>130</v>
+        <v>381</v>
       </c>
       <c r="C677">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B678" t="s">
-        <v>386</v>
+        <v>132</v>
       </c>
       <c r="C678">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B679" t="s">
-        <v>45</v>
+        <v>261</v>
       </c>
       <c r="C679">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B680" t="s">
-        <v>154</v>
+        <v>393</v>
       </c>
       <c r="C680">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B681" t="s">
-        <v>387</v>
+        <v>76</v>
       </c>
       <c r="C681">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B682" t="s">
-        <v>76</v>
+        <v>394</v>
       </c>
       <c r="C682">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B683" t="s">
-        <v>388</v>
+        <v>346</v>
       </c>
       <c r="C683">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B684" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C684">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B685" t="s">
-        <v>87</v>
+        <v>347</v>
       </c>
       <c r="C685">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B686" t="s">
-        <v>116</v>
+        <v>22</v>
       </c>
       <c r="C686">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B687" t="s">
-        <v>303</v>
+        <v>395</v>
       </c>
       <c r="C687">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="688" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B688" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="C688">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="689" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B689" t="s">
-        <v>162</v>
+        <v>88</v>
       </c>
       <c r="C689">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="690" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B690" t="s">
-        <v>334</v>
+        <v>397</v>
       </c>
       <c r="C690">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="691" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B691" t="s">
-        <v>335</v>
+        <v>267</v>
       </c>
       <c r="C691">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="692" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B692" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="C692">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="693" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B693" t="s">
-        <v>254</v>
+        <v>165</v>
       </c>
       <c r="C693">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="694" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B694" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="C694">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B695" t="s">
-        <v>393</v>
+        <v>149</v>
       </c>
       <c r="C695">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="696" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B696" t="s">
-        <v>394</v>
+        <v>41</v>
       </c>
       <c r="C696">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="697" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B697" t="s">
-        <v>395</v>
+        <v>124</v>
       </c>
       <c r="C697">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="698" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B698" t="s">
-        <v>396</v>
+        <v>60</v>
       </c>
       <c r="C698">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="699" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B699" t="s">
-        <v>106</v>
+        <v>7</v>
       </c>
       <c r="C699">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="700" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B700" t="s">
-        <v>292</v>
+        <v>176</v>
       </c>
       <c r="C700">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="701" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B701" t="s">
-        <v>397</v>
+        <v>357</v>
       </c>
       <c r="C701">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="702" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B702" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C702">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="703" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B703" t="s">
-        <v>72</v>
+        <v>402</v>
       </c>
       <c r="C703">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="704" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B704" t="s">
-        <v>47</v>
+        <v>403</v>
       </c>
       <c r="C704">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="705" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B705" t="s">
-        <v>387</v>
+        <v>352</v>
       </c>
       <c r="C705">
         <v>1</v>
@@ -9424,32 +9406,32 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B706" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C706">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="707" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B707" t="s">
-        <v>261</v>
+        <v>107</v>
       </c>
       <c r="C707">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="708" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B708" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="C708">
         <v>1</v>
@@ -9457,10 +9439,10 @@
     </row>
     <row r="709" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B709" t="s">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="C709">
         <v>1</v>
@@ -9468,32 +9450,32 @@
     </row>
     <row r="710" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B710" t="s">
-        <v>400</v>
+        <v>76</v>
       </c>
       <c r="C710">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="711" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B711" t="s">
-        <v>346</v>
+        <v>136</v>
       </c>
       <c r="C711">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="712" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B712" t="s">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="C712">
         <v>1</v>
@@ -9501,197 +9483,197 @@
     </row>
     <row r="713" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B713" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="C713">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="714" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B714" t="s">
-        <v>22</v>
+        <v>405</v>
       </c>
       <c r="C714">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="715" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B715" t="s">
-        <v>401</v>
+        <v>84</v>
       </c>
       <c r="C715">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="716" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B716" t="s">
-        <v>402</v>
+        <v>302</v>
       </c>
       <c r="C716">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B717" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="C717">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="718" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B718" t="s">
-        <v>403</v>
+        <v>116</v>
       </c>
       <c r="C718">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="719" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B719" t="s">
-        <v>267</v>
+        <v>119</v>
       </c>
       <c r="C719">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="720" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B720" t="s">
-        <v>404</v>
+        <v>285</v>
       </c>
       <c r="C720">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="721" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="B721" t="s">
-        <v>165</v>
+        <v>90</v>
       </c>
       <c r="C721">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="722" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B722" t="s">
-        <v>406</v>
+        <v>93</v>
       </c>
       <c r="C722">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="723" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B723" t="s">
-        <v>149</v>
+        <v>307</v>
       </c>
       <c r="C723">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="724" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B724" t="s">
-        <v>41</v>
+        <v>255</v>
       </c>
       <c r="C724">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="725" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B725" t="s">
-        <v>124</v>
+        <v>256</v>
       </c>
       <c r="C725">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="726" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B726" t="s">
-        <v>60</v>
+        <v>233</v>
       </c>
       <c r="C726">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="727" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B727" t="s">
-        <v>7</v>
+        <v>407</v>
       </c>
       <c r="C727">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B728" t="s">
-        <v>176</v>
+        <v>408</v>
       </c>
       <c r="C728">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="729" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B729" t="s">
-        <v>360</v>
+        <v>126</v>
       </c>
       <c r="C729">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="730" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B730" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C730">
         <v>4</v>
@@ -9699,32 +9681,32 @@
     </row>
     <row r="731" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B731" t="s">
-        <v>408</v>
+        <v>127</v>
       </c>
       <c r="C731">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="732" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B732" t="s">
-        <v>409</v>
+        <v>128</v>
       </c>
       <c r="C732">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="733" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B733" t="s">
-        <v>352</v>
+        <v>129</v>
       </c>
       <c r="C733">
         <v>1</v>
@@ -9732,10 +9714,10 @@
     </row>
     <row r="734" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B734" t="s">
-        <v>130</v>
+        <v>410</v>
       </c>
       <c r="C734">
         <v>1</v>
@@ -9743,10 +9725,10 @@
     </row>
     <row r="735" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B735" t="s">
-        <v>107</v>
+        <v>45</v>
       </c>
       <c r="C735">
         <v>4</v>
@@ -9754,10 +9736,10 @@
     </row>
     <row r="736" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B736" t="s">
-        <v>410</v>
+        <v>72</v>
       </c>
       <c r="C736">
         <v>1</v>
@@ -9765,10 +9747,10 @@
     </row>
     <row r="737" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B737" t="s">
-        <v>132</v>
+        <v>47</v>
       </c>
       <c r="C737">
         <v>1</v>
@@ -9776,21 +9758,21 @@
     </row>
     <row r="738" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B738" t="s">
-        <v>76</v>
+        <v>181</v>
       </c>
       <c r="C738">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B739" t="s">
-        <v>136</v>
+        <v>259</v>
       </c>
       <c r="C739">
         <v>1</v>
@@ -9798,10 +9780,10 @@
     </row>
     <row r="740" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B740" t="s">
-        <v>19</v>
+        <v>381</v>
       </c>
       <c r="C740">
         <v>1</v>
@@ -9809,175 +9791,175 @@
     </row>
     <row r="741" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B741" t="s">
-        <v>363</v>
+        <v>132</v>
       </c>
       <c r="C741">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="742" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B742" t="s">
-        <v>411</v>
+        <v>109</v>
       </c>
       <c r="C742">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="743" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B743" t="s">
-        <v>84</v>
+        <v>133</v>
       </c>
       <c r="C743">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="744" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B744" t="s">
-        <v>302</v>
+        <v>76</v>
       </c>
       <c r="C744">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="745" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B745" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="C745">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="746" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B746" t="s">
-        <v>116</v>
+        <v>411</v>
       </c>
       <c r="C746">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="747" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B747" t="s">
-        <v>119</v>
+        <v>412</v>
       </c>
       <c r="C747">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="748" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B748" t="s">
-        <v>285</v>
+        <v>413</v>
       </c>
       <c r="C748">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="749" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B749" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="C749">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="B750" t="s">
-        <v>93</v>
+        <v>298</v>
       </c>
       <c r="C750">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="751" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="B751" t="s">
-        <v>307</v>
+        <v>414</v>
       </c>
       <c r="C751">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="752" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="B752" t="s">
-        <v>255</v>
+        <v>415</v>
       </c>
       <c r="C752">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="753" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="B753" t="s">
-        <v>256</v>
+        <v>284</v>
       </c>
       <c r="C753">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="754" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="B754" t="s">
-        <v>233</v>
+        <v>140</v>
       </c>
       <c r="C754">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="755" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="B755" t="s">
-        <v>413</v>
+        <v>266</v>
       </c>
       <c r="C755">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="756" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="B756" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C756">
         <v>1</v>
@@ -9985,331 +9967,23 @@
     </row>
     <row r="757" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="B757" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="C757">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="758" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="B758" t="s">
-        <v>415</v>
+        <v>143</v>
       </c>
       <c r="C758">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="759" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A759" t="s">
-        <v>412</v>
-      </c>
-      <c r="B759" t="s">
-        <v>127</v>
-      </c>
-      <c r="C759">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="760" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A760" t="s">
-        <v>412</v>
-      </c>
-      <c r="B760" t="s">
-        <v>128</v>
-      </c>
-      <c r="C760">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="761" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A761" t="s">
-        <v>412</v>
-      </c>
-      <c r="B761" t="s">
-        <v>129</v>
-      </c>
-      <c r="C761">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="762" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A762" t="s">
-        <v>412</v>
-      </c>
-      <c r="B762" t="s">
-        <v>416</v>
-      </c>
-      <c r="C762">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="763" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A763" t="s">
-        <v>412</v>
-      </c>
-      <c r="B763" t="s">
-        <v>45</v>
-      </c>
-      <c r="C763">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="764" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A764" t="s">
-        <v>412</v>
-      </c>
-      <c r="B764" t="s">
-        <v>72</v>
-      </c>
-      <c r="C764">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="765" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A765" t="s">
-        <v>412</v>
-      </c>
-      <c r="B765" t="s">
-        <v>47</v>
-      </c>
-      <c r="C765">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="766" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A766" t="s">
-        <v>412</v>
-      </c>
-      <c r="B766" t="s">
-        <v>181</v>
-      </c>
-      <c r="C766">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="767" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A767" t="s">
-        <v>412</v>
-      </c>
-      <c r="B767" t="s">
-        <v>259</v>
-      </c>
-      <c r="C767">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="768" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A768" t="s">
-        <v>412</v>
-      </c>
-      <c r="B768" t="s">
-        <v>387</v>
-      </c>
-      <c r="C768">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="769" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A769" t="s">
-        <v>412</v>
-      </c>
-      <c r="B769" t="s">
-        <v>132</v>
-      </c>
-      <c r="C769">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="770" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A770" t="s">
-        <v>412</v>
-      </c>
-      <c r="B770" t="s">
-        <v>109</v>
-      </c>
-      <c r="C770">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="771" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A771" t="s">
-        <v>412</v>
-      </c>
-      <c r="B771" t="s">
-        <v>133</v>
-      </c>
-      <c r="C771">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="772" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A772" t="s">
-        <v>412</v>
-      </c>
-      <c r="B772" t="s">
-        <v>76</v>
-      </c>
-      <c r="C772">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="773" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A773" t="s">
-        <v>412</v>
-      </c>
-      <c r="B773" t="s">
-        <v>135</v>
-      </c>
-      <c r="C773">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="774" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A774" t="s">
-        <v>412</v>
-      </c>
-      <c r="B774" t="s">
-        <v>417</v>
-      </c>
-      <c r="C774">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="775" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A775" t="s">
-        <v>412</v>
-      </c>
-      <c r="B775" t="s">
-        <v>418</v>
-      </c>
-      <c r="C775">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="776" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A776" t="s">
-        <v>412</v>
-      </c>
-      <c r="B776" t="s">
-        <v>419</v>
-      </c>
-      <c r="C776">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="777" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A777" t="s">
-        <v>412</v>
-      </c>
-      <c r="B777" t="s">
-        <v>111</v>
-      </c>
-      <c r="C777">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="778" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A778" t="s">
-        <v>412</v>
-      </c>
-      <c r="B778" t="s">
-        <v>298</v>
-      </c>
-      <c r="C778">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="779" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A779" t="s">
-        <v>412</v>
-      </c>
-      <c r="B779" t="s">
-        <v>420</v>
-      </c>
-      <c r="C779">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="780" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A780" t="s">
-        <v>412</v>
-      </c>
-      <c r="B780" t="s">
-        <v>421</v>
-      </c>
-      <c r="C780">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="781" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A781" t="s">
-        <v>412</v>
-      </c>
-      <c r="B781" t="s">
-        <v>284</v>
-      </c>
-      <c r="C781">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="782" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A782" t="s">
-        <v>412</v>
-      </c>
-      <c r="B782" t="s">
-        <v>140</v>
-      </c>
-      <c r="C782">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="783" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A783" t="s">
-        <v>412</v>
-      </c>
-      <c r="B783" t="s">
-        <v>266</v>
-      </c>
-      <c r="C783">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="784" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A784" t="s">
-        <v>412</v>
-      </c>
-      <c r="B784" t="s">
-        <v>422</v>
-      </c>
-      <c r="C784">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="785" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A785" t="s">
-        <v>412</v>
-      </c>
-      <c r="B785" t="s">
-        <v>142</v>
-      </c>
-      <c r="C785">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="786" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A786" t="s">
-        <v>412</v>
-      </c>
-      <c r="B786" t="s">
-        <v>143</v>
-      </c>
-      <c r="C786">
         <v>2</v>
       </c>
     </row>
@@ -10320,7 +9994,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -10328,16 +10002,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -10648,120 +10322,103 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B20">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C20">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E20">
-        <v>33.044419642857143</v>
+        <v>54.569132653061217</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B21">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C21">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D21">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E21">
-        <v>54.569132653061217</v>
+        <v>63.55</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B22">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C22">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E22">
-        <v>63.55</v>
+        <v>29.491071428571431</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B23">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C23">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D23">
         <v>5</v>
       </c>
       <c r="E23">
-        <v>29.491071428571431</v>
+        <v>37.964285714285722</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C24">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E24">
-        <v>37.964285714285722</v>
+        <v>43.033035714285717</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B25">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C25">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E25">
-        <v>43.033035714285717</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="B26">
-        <v>37</v>
-      </c>
-      <c r="C26">
-        <v>16</v>
-      </c>
-      <c r="D26">
-        <v>5</v>
-      </c>
-      <c r="E26">
         <v>62.508571428571429</v>
       </c>
     </row>
